--- a/produits/preuves/sortie/xlookup/xlookup.xlsx
+++ b/produits/preuves/sortie/xlookup/xlookup.xlsx
@@ -249,6 +249,7 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10.73"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="0" width="14.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="4.9"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -310,8 +311,10 @@
   <dimension ref="A1:D2"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10.73"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="0" width="14.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6.1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10.51"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="14.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="4.9"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
